--- a/experiment/baseline/BigSleep_Integrity/bigsleep_Integrity_data.xlsx
+++ b/experiment/baseline/BigSleep_Integrity/bigsleep_Integrity_data.xlsx
@@ -1156,7 +1156,7 @@
         <v>25</v>
       </c>
       <c r="H5" s="1">
-        <v>307</v>
+        <v>131</v>
       </c>
       <c r="I5" s="1">
         <v>5</v>
